--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  14.07.2025 a 20.07.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  14.07.2025 a 20.07.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1581" documentId="11_0BC9B2A1CDA062C331AE158982E576033F4F6B40" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{070E3B93-22C0-474B-9019-C205E8A5D555}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED5445DA-F4D4-49AB-8861-48C922675858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="14.07" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="162">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -459,6 +459,90 @@
   </si>
   <si>
     <t xml:space="preserve">SUMARE CENTRO HOTEL LTDA EPP                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAIQUE FONSECA SOARES                        </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 17.07.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E S ROCHA EPP                                </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi (Foto do local incorreto.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRITAS IPIAU LTDA ME                         </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Direita (Lateral direita não enquadrada corretamente). Foto 45º - Frente e Lateral Esquerda (Lateral esquerda não enquadrada corretamente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTEIRO DOCES E EMBALAGENS LTDA EPP         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISAIAS GABRIEL DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON SANTOS LIMA                        </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Hodômetro (Foto Cortando Parte do Hodômetro). Porta malas (Com objetos dentro).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOURA FRIOS COMERCIO DE ALIMENTOS LTDA ME    </t>
+  </si>
+  <si>
+    <t>Por gentileza nos enviar cópia da NF p/enquadramento correto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEREZINHA FERREIRA DOS SANTOS                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISLAINE CANDIDA JOSE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAIK GEOVANNY DOMINGUES BORGES               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO BARBOSA DE SOUZA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO OLIVEIRA DOS SANTOS             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLAS GASPAR PONTES                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMIRANDA REPRESENTACOES COMERCIAIS LTDA ME   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILEIDE CARVALHO DE SOUZA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIMILTON FERREIRA DOS SANTOS                </t>
+  </si>
+  <si>
+    <t>Santander - Veículo em duplicidade com proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANALDO VIEIRA DOS ANJOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARLES ALBERT SEGECS ME                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHELE APARECIDA BORGES ROSSI               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMERSON DA SILVA COSTA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRA MARIA ALVES DA SILVA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONES DE OLIVEIRA DO PRADO                   </t>
   </si>
 </sst>
 </file>
@@ -716,7 +800,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -801,9 +885,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -819,17 +900,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -4104,7 +4198,7 @@
       <c r="E2" s="8">
         <v>3450028362</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="41" t="s">
         <v>105</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -4130,7 +4224,7 @@
       <c r="E3" s="20">
         <v>3450029968</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="36" t="s">
         <v>107</v>
       </c>
       <c r="G3" s="32" t="s">
@@ -4144,7 +4238,7 @@
       <c r="A4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="40">
         <v>45848</v>
       </c>
       <c r="C4" s="7">
@@ -4153,16 +4247,16 @@
       <c r="D4" s="33">
         <v>133366990</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="39">
         <v>3450026536</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="21" t="s">
         <v>109</v>
       </c>
       <c r="I4" s="26">
@@ -4173,7 +4267,7 @@
       <c r="A5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="40">
         <v>45847</v>
       </c>
       <c r="C5" s="7">
@@ -4182,16 +4276,16 @@
       <c r="D5" s="33">
         <v>133343731</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="39">
         <v>3450025315</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="36" t="s">
         <v>111</v>
       </c>
       <c r="I5" s="26">
@@ -4208,13 +4302,13 @@
       <c r="C6" s="7">
         <v>45855</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="25">
         <v>133424619</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="37">
         <v>3450029220</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="12" t="s">
         <v>112</v>
       </c>
       <c r="G6" s="30" t="s">
@@ -4237,13 +4331,13 @@
       <c r="C7" s="7">
         <v>45855</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="25">
         <v>133425743</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="37">
         <v>3450025403</v>
       </c>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="12" t="s">
         <v>113</v>
       </c>
       <c r="G7" s="30" t="s">
@@ -4266,13 +4360,13 @@
       <c r="C8" s="7">
         <v>45855</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="25">
         <v>133345038</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="37">
         <v>3450025359</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="12" t="s">
         <v>115</v>
       </c>
       <c r="G8" s="30" t="s">
@@ -4295,13 +4389,13 @@
       <c r="C9" s="7">
         <v>45855</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="25">
         <v>133450029</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="37">
         <v>3450026030</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="12" t="s">
         <v>116</v>
       </c>
       <c r="G9" s="30" t="s">
@@ -4324,19 +4418,19 @@
       <c r="C10" s="7">
         <v>45855</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="25">
         <v>133436196</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="37">
         <v>3450029616</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="12" t="s">
         <v>117</v>
       </c>
       <c r="G10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I10" s="26">
@@ -4353,19 +4447,19 @@
       <c r="C11" s="7">
         <v>45855</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="25">
         <v>133457404</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="37">
         <v>3450030573</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="12" t="s">
         <v>118</v>
       </c>
       <c r="G11" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I11" s="26">
@@ -4382,19 +4476,19 @@
       <c r="C12" s="7">
         <v>45855</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="25">
         <v>133467509</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="37">
         <v>3450031211</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="26">
@@ -4411,16 +4505,16 @@
       <c r="C13" s="7">
         <v>45855</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="25">
         <v>133274775</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="34">
         <v>3450022103</v>
       </c>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="38" t="s">
         <v>13</v>
       </c>
       <c r="H13" s="15" t="s">
@@ -4440,13 +4534,13 @@
       <c r="C14" s="7">
         <v>45855</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="25">
         <v>133475431</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="35">
         <v>3450031574</v>
       </c>
-      <c r="F14" s="43" t="s">
+      <c r="F14" s="12" t="s">
         <v>120</v>
       </c>
       <c r="G14" s="31" t="s">
@@ -4469,19 +4563,19 @@
       <c r="C15" s="7">
         <v>45855</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="25">
         <v>133374552</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="35">
         <v>3450026932</v>
       </c>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="12" t="s">
         <v>121</v>
       </c>
       <c r="G15" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="9" t="s">
         <v>122</v>
       </c>
       <c r="I15" s="26">
@@ -4498,19 +4592,19 @@
       <c r="C16" s="7">
         <v>45855</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="25">
         <v>133283832</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="35">
         <v>3450022554</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="12" t="s">
         <v>123</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="9" t="s">
         <v>124</v>
       </c>
       <c r="I16" s="26">
@@ -4527,19 +4621,19 @@
       <c r="C17" s="7">
         <v>45855</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="25">
         <v>133271654</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="35">
         <v>3450021894</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="9" t="s">
         <v>126</v>
       </c>
       <c r="I17" s="26">
@@ -4556,13 +4650,13 @@
       <c r="C18" s="7">
         <v>45855</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="25">
         <v>133338929</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="35">
         <v>3450025161</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="12" t="s">
         <v>127</v>
       </c>
       <c r="G18" s="31" t="s">
@@ -4585,13 +4679,13 @@
       <c r="C19" s="7">
         <v>45855</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="25">
         <v>133338951</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="35">
         <v>3450025172</v>
       </c>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="12" t="s">
         <v>128</v>
       </c>
       <c r="G19" s="31" t="s">
@@ -4614,13 +4708,13 @@
       <c r="C20" s="7">
         <v>45855</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="25">
         <v>133351843</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="35">
         <v>3450025777</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="12" t="s">
         <v>129</v>
       </c>
       <c r="G20" s="31" t="s">
@@ -4643,13 +4737,13 @@
       <c r="C21" s="7">
         <v>45855</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="25">
         <v>133349867</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="35">
         <v>3450025579</v>
       </c>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="12" t="s">
         <v>130</v>
       </c>
       <c r="G21" s="31" t="s">
@@ -4672,13 +4766,13 @@
       <c r="C22" s="7">
         <v>45855</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="25">
         <v>133350572</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="35">
         <v>3450025601</v>
       </c>
-      <c r="F22" s="43" t="s">
+      <c r="F22" s="12" t="s">
         <v>131</v>
       </c>
       <c r="G22" s="31" t="s">
@@ -4701,13 +4795,13 @@
       <c r="C23" s="7">
         <v>45855</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="25">
         <v>133351673</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="35">
         <v>3450025700</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="12" t="s">
         <v>132</v>
       </c>
       <c r="G23" s="31" t="s">
@@ -4730,13 +4824,13 @@
       <c r="C24" s="7">
         <v>45855</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="25">
         <v>133352035</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="35">
         <v>3450025799</v>
       </c>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="12" t="s">
         <v>133</v>
       </c>
       <c r="G24" s="31" t="s">
@@ -5084,13 +5178,13 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="17" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.7109375" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5123,229 +5217,483 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="B2" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C2" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D2" s="45">
+        <v>133316645</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450023819</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="I2" s="26">
+        <v>45855</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="B3" s="7">
+        <v>45849</v>
+      </c>
+      <c r="C3" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D3" s="45">
+        <v>133398321</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450028120</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="26">
+        <v>45849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="B4" s="7">
+        <v>45849</v>
+      </c>
+      <c r="C4" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D4" s="45">
+        <v>133388251</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450027559</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="26">
+        <v>45849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="B5" s="7">
+        <v>45849</v>
+      </c>
+      <c r="C5" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D5" s="45">
+        <v>133396557</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450027999</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="26">
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45854</v>
+      </c>
+      <c r="C6" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D6" s="45">
+        <v>133453084</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450030342</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="26">
+        <v>45854</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C7" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D7" s="45">
+        <v>133375356</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450026998</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45855</v>
+      </c>
+      <c r="C8" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D8" s="45">
+        <v>133482585</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450031960</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="26">
+        <v>45855</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45849</v>
+      </c>
+      <c r="C9" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D9" s="45">
+        <v>133389633</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450027603</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="I9" s="26">
+        <v>45849</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45845</v>
+      </c>
+      <c r="C10" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D10" s="45">
+        <v>133302725</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450023478</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C11" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D11" s="45">
+        <v>133361215</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450026118</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C12" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D12" s="45">
+        <v>133363825</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450026327</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C13" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D13" s="45">
+        <v>133365693</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450026470</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C14" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D14" s="45">
+        <v>133366936</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450026525</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="B15" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C15" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D15" s="45">
+        <v>133369748</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450026668</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="26">
+        <v>45848</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="44" customFormat="1" ht="16.5" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="40">
+        <v>45848</v>
+      </c>
+      <c r="C16" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D16" s="45">
+        <v>133373236</v>
+      </c>
+      <c r="E16" s="46">
+        <v>3450026822</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="47">
+        <v>45848</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="7">
+        <v>45848</v>
+      </c>
+      <c r="C17" s="19">
+        <v>45856</v>
+      </c>
+      <c r="D17" s="45">
+        <v>133373368</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450026877</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="26">
+        <v>45848</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
@@ -5353,7 +5701,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5727,7 +6075,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5745,17 +6093,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5792,255 +6140,376 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C2" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D2" s="25">
+        <v>133321398</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450024061</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45860</v>
+      </c>
+      <c r="C3" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D3" s="25">
+        <v>133332609</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450024919</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I3" s="26">
+        <v>45860</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C4" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D4" s="25">
+        <v>133322043</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450024116</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45842</v>
+      </c>
+      <c r="C5" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D5" s="25">
+        <v>133284117</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450022565</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="26">
+        <v>45855</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C6" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D6" s="25">
+        <v>133323954</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450024292</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C7" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D7" s="25">
+        <v>133324576</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450024369</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C8" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D8" s="25">
+        <v>133323145</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450024204</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45845</v>
+      </c>
+      <c r="C9" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D9" s="25">
+        <v>133317324</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450023357</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="26">
+        <v>45845</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45846</v>
+      </c>
+      <c r="C10" s="19">
+        <v>45857</v>
+      </c>
+      <c r="D10" s="25">
+        <v>133321828</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450024094</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="26">
+        <v>45846</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="43"/>
       <c r="G11" s="6"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="6"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="6"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="6"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="6"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="1:9">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:8">
       <c r="A21" s="6"/>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:8">
       <c r="A22" s="6"/>
       <c r="B22" s="8"/>
       <c r="C22" s="7"/>
@@ -6050,7 +6519,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:8">
       <c r="A23" s="6"/>
       <c r="B23" s="8"/>
       <c r="C23" s="7"/>
@@ -6060,7 +6529,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="7"/>
@@ -6070,7 +6539,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:8">
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
@@ -6080,7 +6549,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:8">
       <c r="A26" s="6"/>
       <c r="B26" s="8"/>
       <c r="C26" s="7"/>
@@ -6090,7 +6559,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:8">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="7"/>
@@ -6100,7 +6569,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:8">
       <c r="A28" s="6"/>
       <c r="B28" s="8"/>
       <c r="C28" s="7"/>
@@ -6110,7 +6579,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29" s="6"/>
       <c r="B29" s="8"/>
       <c r="C29" s="7"/>
@@ -6120,7 +6589,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30" s="6"/>
       <c r="B30" s="8"/>
       <c r="C30" s="7"/>
@@ -6130,7 +6599,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" s="6"/>
       <c r="B31" s="8"/>
       <c r="C31" s="7"/>
@@ -6140,7 +6609,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -6300,107 +6769,17 @@
       <c r="G47" s="6"/>
       <c r="H47" s="9"/>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A10" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7113,65 +7492,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-477956</_dlc_DocId>
@@ -7214,7 +7534,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7586,18 +7906,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710A484D-A36D-43F1-A571-16D411D0AE20}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710A484D-A36D-43F1-A571-16D411D0AE20}"/>
 </file>